--- a/business_surveys/048_property_sustainability_awareness_survey--business_surveys.xlsx
+++ b/business_surveys/048_property_sustainability_awareness_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -1347,34 +1347,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sustainability_features_choices</t>
+          <t>current_level_of_sustainability_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>green_roofs</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Green Roofs</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sustainability_features_choices</t>
+          <t>current_level_of_sustainability_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>energy_efficiency</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Energy Efficiency</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1386,46 +1386,46 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>current_level_of_sustainability_choices</t>
+          <t>target_level_of_sustainability_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>current_level_of_sustainability_choices</t>
+          <t>target_level_of_sustainability_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1437,46 +1437,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>target_level_of_sustainability_choices</t>
+          <t>priority_for_improvement_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>target_level_of_sustainability_choices</t>
+          <t>priority_for_improvement_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1488,46 +1488,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>priority_for_improvement_choices</t>
+          <t>communication_channels_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>priority_for_improvement_choices</t>
+          <t>communication_channels_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1573,80 +1573,80 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>sustainability_team_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>in_person</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>In Person</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>sustainability_team_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sustainability_team_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>office_building</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Office Building</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sustainability_team_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>residential_building</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Residential Building</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>office_building</t>
+          <t>commercial_building</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Office Building</t>
+          <t>Commercial Building</t>
         </is>
       </c>
     </row>
@@ -1675,46 +1675,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>residential_building</t>
+          <t>industrial_building</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Residential Building</t>
+          <t>Industrial Building</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>energy_rating_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>commercial_building</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Commercial Building</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>energy_rating_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>industrial_building</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Industrial Building</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1726,46 +1726,46 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>energy_rating_choices</t>
+          <t>water_rating_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>energy_rating_choices</t>
+          <t>water_rating_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1777,46 +1777,46 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>water_rating_choices</t>
+          <t>waste_rating_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>water_rating_choices</t>
+          <t>waste_rating_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1828,46 +1828,46 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>waste_rating_choices</t>
+          <t>carbon_footprint_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>waste_rating_choices</t>
+          <t>carbon_footprint_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1879,46 +1879,46 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>carbon_footprint_choices</t>
+          <t>green_building_certification_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>leed</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>LEED</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>carbon_footprint_choices</t>
+          <t>green_building_certification_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>energy_star</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Energy Star</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>leed</t>
+          <t>well</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LEED</t>
+          <t>WELL</t>
         </is>
       </c>
     </row>
@@ -1947,46 +1947,46 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>energy_star</t>
+          <t>envirole</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Energy Star</t>
+          <t>Envirole</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>green_building_certification_choices</t>
+          <t>sustainability_features_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>well</t>
+          <t>green_walls</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>Green Walls</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>green_building_certification_choices</t>
+          <t>sustainability_features_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>envirole</t>
+          <t>green_roofs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Envirole</t>
+          <t>Green Roofs</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>green_walls</t>
+          <t>solar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Green Walls</t>
+          <t>Solar</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>green_roofs</t>
+          <t>energy_efficiency</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Green Roofs</t>
+          <t>Energy Efficiency</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>solar</t>
+          <t>water_conservation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Solar</t>
+          <t>Water Conservation</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>energy_efficiency</t>
+          <t>waste_management</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Energy Efficiency</t>
+          <t>Waste Management</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>water_conservation</t>
+          <t>recycling</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Water Conservation</t>
+          <t>Recycling</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>waste_management</t>
+          <t>rainwater_harvesting</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Waste Management</t>
+          <t>Rainwater Harvesting</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>recycling</t>
+          <t>greenhouse_gas_reduction</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Recycling</t>
+          <t>Greenhouse Gas Reduction</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>energy_efficiency</t>
+          <t>green_infrastructure</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Energy Efficiency</t>
+          <t>Green Infrastructure</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>rainwater_harvesting</t>
+          <t>high_performance_glazing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rainwater Harvesting</t>
+          <t>High Performance Glazing</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>greenhouse_gas_reduction</t>
+          <t>high_performance_insulation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Reduction</t>
+          <t>High Performance Insulation</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>green_infrastructure</t>
+          <t>high_performance_windows</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Green Infrastructure</t>
+          <t>High Performance Windows</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>high_performance_glazing</t>
+          <t>high_performance_doors</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>High Performance Glazing</t>
+          <t>High Performance Doors</t>
         </is>
       </c>
     </row>
@@ -2202,61 +2202,10 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>high_performance_insulation</t>
+          <t>high_performance_roofing</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
-        <is>
-          <t>High Performance Insulation</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>sustainability_features_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>high_performance_windows</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>High Performance Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>sustainability_features_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>high_performance_doors</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>High Performance Doors</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>sustainability_features_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>high_performance_roofing</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
         <is>
           <t>High Performance Roofing</t>
         </is>
